--- a/AAII_Financials/Quarterly/AAGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AAGRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
   <si>
     <t>AAGRY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,61 +656,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -738,8 +742,11 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -767,8 +774,11 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,8 +806,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,8 +822,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -838,8 +852,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,8 +884,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -896,8 +916,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +948,11 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,8 +961,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -964,8 +991,11 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -993,8 +1023,11 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,8 +1039,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1035,8 +1069,11 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1064,8 +1101,11 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1093,8 +1133,11 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1122,8 +1165,11 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1197,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,8 +1229,11 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1209,8 +1261,11 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1238,8 +1293,11 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1325,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1357,11 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1389,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,8 +1421,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1383,8 +1453,11 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1412,8 +1485,11 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,8 +1517,11 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1470,42 +1549,48 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1602,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,37 +1616,41 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>322400</v>
+      </c>
+      <c r="E41" s="3">
         <v>201000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>288400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>243900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>193500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>135600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>163000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>88700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>127900</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,211 +1678,235 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E43" s="3">
         <v>25500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>46900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>66400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>60900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>57000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>63200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>58100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>51600</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>205800</v>
+      </c>
+      <c r="E44" s="3">
         <v>247300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>173300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>176500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>186000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>202600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>212600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>260000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>224300</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E45" s="3">
         <v>50000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>39900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>62900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>66700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>65700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>53500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>598600</v>
+      </c>
+      <c r="E46" s="3">
         <v>523900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>548600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>520000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>503200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>461800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>504500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>460300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>510800</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E47" s="3">
         <v>25500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>25200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>26600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>28300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>33800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>34000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>40700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>42100</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1040100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1082700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1172600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1091600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1134300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1174600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1155500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1190500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1195200</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E49" s="3">
         <v>3500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3500</v>
-      </c>
-      <c r="H49" s="3">
-        <v>3600</v>
       </c>
       <c r="I49" s="3">
         <v>3600</v>
       </c>
       <c r="J49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="K49" s="3">
         <v>3700</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +1934,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +1966,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>99300</v>
+      </c>
+      <c r="E52" s="3">
         <v>122300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>138900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>140500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>163200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>166300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>165500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>214100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>170200</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2030,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1796800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1788600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1922600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1813600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1864100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1871400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1898700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1945900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1964600</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2078,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,182 +2092,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E57" s="3">
         <v>44200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>53800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>56200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>59100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>54600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>63800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>92800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>66100</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E58" s="3">
         <v>105000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>106000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>150900</v>
-      </c>
-      <c r="G58" s="3">
-        <v>150200</v>
       </c>
       <c r="H58" s="3">
         <v>150200</v>
       </c>
       <c r="I58" s="3">
+        <v>150200</v>
+      </c>
+      <c r="J58" s="3">
         <v>150700</v>
-      </c>
-      <c r="J58" s="3">
-        <v>300</v>
       </c>
       <c r="K58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E59" s="3">
         <v>36600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>50000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>35500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>38000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>44200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>38100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>237000</v>
+      </c>
+      <c r="E60" s="3">
         <v>201100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>257100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>272800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>271400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>251900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>297800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>160800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>136500</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>90600</v>
+      </c>
+      <c r="E61" s="3">
         <v>93200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>105000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>103300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>106600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>109600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>109500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>262700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>264000</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300</v>
+      </c>
+      <c r="E62" s="3">
         <v>500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2000</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>5300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2314,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2346,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2378,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>379900</v>
+      </c>
+      <c r="E66" s="3">
         <v>347300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>410000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>422200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>424900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>407400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>458500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>481500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>461300</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2426,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2456,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2488,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2520,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2552,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1093700</v>
+      </c>
+      <c r="E72" s="3">
         <v>1107800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1158600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1064500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1100700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1117100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1095500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1110600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1146100</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2616,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2648,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2680,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1384100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1406500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1476200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1358200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1404000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1428300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1405100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1429300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1465700</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,42 +2744,48 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2618,8 +2813,11 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +2829,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E83" s="3">
         <v>25500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>21200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>20400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +2891,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +2923,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +2955,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +2987,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3019,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>139900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-39100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>90300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>94500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>69200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>96400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>28400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>23600</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3067,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12400</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3129,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3161,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-28600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,37 +3209,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3">
         <v>10000</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>19400</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
         <v>10200</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>40900</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3271,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3303,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,91 +3335,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-46400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-25600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-15100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-48000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-70200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>25000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>56300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>61700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-28100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>77000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-38700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>19600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AAGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AAGRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>AAGRY</t>
   </si>
@@ -656,65 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,8 +749,11 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -777,8 +784,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +819,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +836,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,8 +869,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,8 +904,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -919,8 +939,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -951,8 +974,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,8 +988,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -994,8 +1021,11 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1026,8 +1056,11 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,8 +1073,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1072,8 +1106,11 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1104,8 +1141,11 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1136,8 +1176,11 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1168,8 +1211,11 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1200,8 +1246,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,8 +1281,11 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1264,8 +1316,11 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1296,8 +1351,11 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1386,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1421,11 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1456,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,8 +1491,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1456,8 +1526,11 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1488,8 +1561,11 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,8 +1596,11 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1552,45 +1631,51 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1688,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,40 +1703,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>389600</v>
+      </c>
+      <c r="E41" s="3">
         <v>322400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>201000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>288400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>243900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>193500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>135600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>163000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>88700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>127900</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1681,136 +1771,151 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E43" s="3">
         <v>36400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>46900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>66400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>60900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>57000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>63200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>58100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>51600</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>219700</v>
+      </c>
+      <c r="E44" s="3">
         <v>205800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>247300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>173300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>176500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>186000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>202600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>212600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>260000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>224300</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E45" s="3">
         <v>34000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>50000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>39900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>62900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>66700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>65700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>53500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>703100</v>
+      </c>
+      <c r="E46" s="3">
         <v>598600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>523900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>548600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>520000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>503200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>461800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>504500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>460300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>510800</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1818,63 +1923,69 @@
         <v>22400</v>
       </c>
       <c r="E47" s="3">
+        <v>22400</v>
+      </c>
+      <c r="F47" s="3">
         <v>25500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>25200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>26600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>28300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>33800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>34000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>40700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>42100</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1048600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1040100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1082700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1172600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1091600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1134300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1174600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1155500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1190500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1195200</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1882,31 +1993,34 @@
         <v>3400</v>
       </c>
       <c r="E49" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F49" s="3">
         <v>3500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3500</v>
-      </c>
-      <c r="I49" s="3">
-        <v>3600</v>
       </c>
       <c r="J49" s="3">
         <v>3600</v>
       </c>
       <c r="K49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="L49" s="3">
         <v>3700</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2051,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2086,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E52" s="3">
         <v>99300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>122300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>138900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>140500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>163200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>166300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>165500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>214100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>170200</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2156,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1879200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1796800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1788600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1922600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1813600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1864100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1871400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1898700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1945900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1964600</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2208,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,200 +2223,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E57" s="3">
         <v>45900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>44200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>53800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>56200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>59100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>54600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>63800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>92800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>66100</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>104100</v>
+      </c>
+      <c r="E58" s="3">
         <v>102000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>105000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>106000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>150900</v>
-      </c>
-      <c r="H58" s="3">
-        <v>150200</v>
       </c>
       <c r="I58" s="3">
         <v>150200</v>
       </c>
       <c r="J58" s="3">
+        <v>150200</v>
+      </c>
+      <c r="K58" s="3">
         <v>150700</v>
-      </c>
-      <c r="K58" s="3">
-        <v>300</v>
       </c>
       <c r="L58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E59" s="3">
         <v>56500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>36600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>50000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>35500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>38000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>34000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>44200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>280700</v>
+      </c>
+      <c r="E60" s="3">
         <v>237000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>201100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>257100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>272800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>271400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>251900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>297800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>160800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>136500</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>92400</v>
+      </c>
+      <c r="E61" s="3">
         <v>90600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>93200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>105000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>103300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>106600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>109600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>109500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>262700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>264000</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
         <v>300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>5300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2466,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2501,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2536,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>428500</v>
+      </c>
+      <c r="E66" s="3">
         <v>379900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>347300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>410000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>422200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>424900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>407400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>458500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>481500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>461300</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2588,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2621,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2656,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2691,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2726,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1120100</v>
+      </c>
+      <c r="E72" s="3">
         <v>1093700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1107800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1158600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1064500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1100700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1117100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1095500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1110600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1146100</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2796,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2831,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +2866,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1416200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1384100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1406500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1476200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1358200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1404000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1428300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1405100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1429300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1465700</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,45 +2936,51 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2816,8 +3011,11 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,40 +3028,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E83" s="3">
         <v>21500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>21500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>21200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3096,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3131,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3166,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3201,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3236,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E89" s="3">
         <v>139900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-39100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>90300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>94500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>69200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>96400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>28400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>23600</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3288,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-28600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12400</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3356,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3391,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-20700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-28600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,40 +3443,44 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3">
         <v>10000</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>19400</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>10200</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>40900</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3511,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3546,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,100 +3581,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-46400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-25600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-15100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-48000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>2500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E102" s="3">
         <v>127000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-70200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>25000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>56300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>61700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-28100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>77000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-38700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>19600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AAGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AAGRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
   <si>
     <t>AAGRY</t>
   </si>
@@ -656,73 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -759,8 +762,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -797,8 +803,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +844,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,8 +863,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,8 +902,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,8 +943,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -965,8 +984,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1025,11 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,8 +1041,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1054,8 +1080,11 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1092,8 +1121,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,8 +1140,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1146,8 +1179,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1184,8 +1220,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1222,8 +1261,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1260,8 +1302,11 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1298,8 +1343,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,8 +1384,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1374,8 +1425,11 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1412,8 +1466,11 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1548,11 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,8 +1630,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1602,8 +1671,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1640,8 +1712,11 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,8 +1753,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1716,51 +1794,57 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,46 +1876,50 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E41" s="3">
         <v>295300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>389600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>322400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>201000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>288400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>243900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>193500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>135600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>163000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>88700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>127900</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1867,241 +1956,262 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E43" s="3">
         <v>29300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>52000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>36400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>25500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>46900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>66400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>60900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>57000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>63200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>58100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>51600</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>216100</v>
+      </c>
+      <c r="E44" s="3">
         <v>177400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>219700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>205800</v>
       </c>
-      <c r="G44" s="3">
-        <v>247300</v>
-      </c>
       <c r="H44" s="3">
+        <v>250100</v>
+      </c>
+      <c r="I44" s="3">
         <v>173300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>176500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>186000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>202600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>212600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>260000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>224300</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E45" s="3">
         <v>44300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>41800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>34000</v>
       </c>
-      <c r="G45" s="3">
-        <v>50000</v>
-      </c>
       <c r="H45" s="3">
+        <v>47200</v>
+      </c>
+      <c r="I45" s="3">
         <v>39900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>62900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>66700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>65700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>53500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>518600</v>
+      </c>
+      <c r="E46" s="3">
         <v>546300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>703100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>598600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>523900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>548600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>520000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>503200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>461800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>504500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>460300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>510800</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E47" s="3">
         <v>21200</v>
-      </c>
-      <c r="E47" s="3">
-        <v>22400</v>
       </c>
       <c r="F47" s="3">
         <v>22400</v>
       </c>
       <c r="G47" s="3">
+        <v>22400</v>
+      </c>
+      <c r="H47" s="3">
         <v>25500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>25200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>26600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>33800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>34000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>40700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>42100</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>979200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1003600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1048600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1040100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1082700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1172600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1091600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1134300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1174600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1155500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1190500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1195200</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="E49" s="3">
         <v>3400</v>
@@ -2110,31 +2220,34 @@
         <v>3400</v>
       </c>
       <c r="G49" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H49" s="3">
         <v>3500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3500</v>
-      </c>
-      <c r="K49" s="3">
-        <v>3600</v>
       </c>
       <c r="L49" s="3">
         <v>3600</v>
       </c>
       <c r="M49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="N49" s="3">
         <v>3700</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,46 +2325,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E52" s="3">
         <v>68800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>72700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>99300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>122300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>138900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>140500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>163200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>166300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>165500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>214100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>170200</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1619200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1675300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1879200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1796800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1788600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1922600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1813600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1864100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1871400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1898700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1945900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1964600</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,160 +2484,173 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E57" s="3">
         <v>48000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>62700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>45900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>44200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>53800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>56200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>59100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>54600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>63800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>92800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>66100</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>5400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>104100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>102000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>105000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>106000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>150900</v>
-      </c>
-      <c r="J58" s="3">
-        <v>150200</v>
       </c>
       <c r="K58" s="3">
         <v>150200</v>
       </c>
       <c r="L58" s="3">
+        <v>150200</v>
+      </c>
+      <c r="M58" s="3">
         <v>150700</v>
-      </c>
-      <c r="M58" s="3">
-        <v>300</v>
       </c>
       <c r="N58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E59" s="3">
         <v>56300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>36100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>56500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>36600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>50000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>35500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>38000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>34000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>44200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>38100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>119800</v>
+      </c>
+      <c r="E60" s="3">
         <v>200400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>280700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>237000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>201100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>257100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>272800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>271400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>251900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>297800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>160800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>136500</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2516,75 +2658,81 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>92400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>90600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>93200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>105000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>103300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>106600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>109600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>109500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>262700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>264000</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
         <v>200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>5300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E66" s="3">
         <v>255500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>428500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>379900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>347300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>410000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>422200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>424900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>407400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>458500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>481500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>461300</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1122400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1097200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1120100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1093700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1107800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1158600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1064500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1100700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1117100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1095500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1110600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1146100</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1410200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1385200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1416200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1384100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1406500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1476200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1358200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1404000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1428300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1405100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1429300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1465700</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,51 +3319,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3212,8 +3406,11 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,46 +3425,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E83" s="3">
         <v>23100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>25500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>21300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-92500</v>
+      </c>
+      <c r="E89" s="3">
         <v>114400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>94400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>139900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-39100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>90300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>94500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>69200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>96400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>23600</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,46 +3729,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-28600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12400</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-20700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,46 +3910,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>14200</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>21800</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
         <v>10000</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>19400</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>10200</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>40900</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,118 +4072,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-189200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-26400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-46400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-25600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-15100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-48000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-130100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-83600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>60800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>127000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-70200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>25000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>56300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>61700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>77000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-38700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AAGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AAGRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
   <si>
     <t>AAGRY</t>
   </si>
@@ -656,76 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,8 +769,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,8 +813,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +963,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1007,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,8 +1068,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1083,8 +1110,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1124,8 +1154,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,8 +1174,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1182,8 +1216,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1223,8 +1260,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1264,8 +1304,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1305,8 +1348,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1392,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,8 +1436,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1428,8 +1480,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1469,8 +1524,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,8 +1700,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1674,8 +1744,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1715,8 +1788,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,8 +1832,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1797,54 +1876,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,49 +1963,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>277500</v>
+      </c>
+      <c r="E41" s="3">
         <v>165000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>295300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>389600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>322400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>201000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>288400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>243900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>193500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>135600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>163000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>88700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>127900</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,254 +2049,275 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E43" s="3">
         <v>74100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>29300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>52000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>36400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>66400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>60900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>57000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>63200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>58100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>51600</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>184200</v>
+      </c>
+      <c r="E44" s="3">
         <v>216100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>177400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>219700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>205800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>250100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>173300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>176500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>186000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>202600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>212600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>260000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>224300</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E45" s="3">
         <v>63400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>44300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>41800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>47200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>39900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>62900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>66700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>65700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>53500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>107000</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>576400</v>
+      </c>
+      <c r="E46" s="3">
         <v>518600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>546300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>703100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>598600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>523900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>548600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>520000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>503200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>461800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>504500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>460300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>510800</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E47" s="3">
         <v>19900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>21200</v>
-      </c>
-      <c r="F47" s="3">
-        <v>22400</v>
       </c>
       <c r="G47" s="3">
         <v>22400</v>
       </c>
       <c r="H47" s="3">
+        <v>22400</v>
+      </c>
+      <c r="I47" s="3">
         <v>25500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>25200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>26600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>33800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>34000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>40700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>42100</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>951200</v>
+      </c>
+      <c r="E48" s="3">
         <v>979200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1003600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1048600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1040100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1082700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1172600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1091600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1134300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1174600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1155500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1190500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1195200</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2214,7 +2325,7 @@
         <v>3300</v>
       </c>
       <c r="E49" s="3">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="F49" s="3">
         <v>3400</v>
@@ -2223,31 +2334,34 @@
         <v>3400</v>
       </c>
       <c r="H49" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I49" s="3">
         <v>3500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3500</v>
-      </c>
-      <c r="L49" s="3">
-        <v>3600</v>
       </c>
       <c r="M49" s="3">
         <v>3600</v>
       </c>
       <c r="N49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="O49" s="3">
         <v>3700</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,49 +2445,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E52" s="3">
         <v>67800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>68800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>72700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>99300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>122300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>138900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>140500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>163200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>166300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>165500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>214100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>170200</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1645500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1619200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1675300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1879200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1796800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1788600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1922600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1813600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1864100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1871400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1898700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1945900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1964600</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,49 +2615,53 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E57" s="3">
         <v>54600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>48000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>62700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>45900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>44200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>53800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>56200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>59100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>54600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>63800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>92800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>66100</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2535,122 +2669,131 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>5400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>104100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>102000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>105000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>106000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>150900</v>
-      </c>
-      <c r="K58" s="3">
-        <v>150200</v>
       </c>
       <c r="L58" s="3">
         <v>150200</v>
       </c>
       <c r="M58" s="3">
+        <v>150200</v>
+      </c>
+      <c r="N58" s="3">
         <v>150700</v>
-      </c>
-      <c r="N58" s="3">
-        <v>300</v>
       </c>
       <c r="O58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E59" s="3">
         <v>52400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>56300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>36100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>56500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>36600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>50000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>35500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>34000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>44200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>38100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>47900</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>144100</v>
+      </c>
+      <c r="E60" s="3">
         <v>119800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>200400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>280700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>237000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>201100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>257100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>272800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>271400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>251900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>297800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>160800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>136500</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2661,78 +2804,84 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>92400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>90600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>93200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>105000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>103300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>106600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>109600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>109500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>262700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>264000</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>5300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>198200</v>
+      </c>
+      <c r="E66" s="3">
         <v>173000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>255500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>428500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>379900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>347300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>410000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>422200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>424900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>407400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>458500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>481500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>461300</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1127300</v>
+      </c>
+      <c r="E72" s="3">
         <v>1122400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1097200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1120100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1093700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1107800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1158600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1064500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1100700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1117100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1095500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1110600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1146100</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1410900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1410200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1385200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1416200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1384100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1406500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1476200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1358200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1404000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1428300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1405100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1429300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1465700</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,54 +3511,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3409,8 +3604,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,49 +3624,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E83" s="3">
         <v>25000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>23100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>21500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>25500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>122900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-92500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>114400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>94400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>139900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-39100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>90300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>94500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>69200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>96400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>28400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>23600</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,49 +3950,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-28600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12400</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-20700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-28600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,49 +4144,53 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3">
         <v>14200</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>21800</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
         <v>10000</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>19400</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3">
         <v>10200</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>40900</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,127 +4318,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-19600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-189200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-26400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-46400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-25600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-15100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-48000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E101" s="3">
         <v>3400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>114900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-130100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-83600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>60800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>127000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-70200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>56300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>61700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-28100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>77000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-38700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19600</v>
       </c>
     </row>
